--- a/Caracterizacion_Haces/data/z8mm-852.xlsx
+++ b/Caracterizacion_Haces/data/z8mm-852.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\14-10-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\15-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="160">
   <si>
     <t>*** BeamMaster USB Measurement system, Version 1.5.0.3 ***</t>
   </si>
@@ -128,367 +128,382 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>-721,5</t>
-  </si>
-  <si>
-    <t>92,20</t>
+    <t>745,3</t>
+  </si>
+  <si>
+    <t>96,20</t>
+  </si>
+  <si>
+    <t>113,1</t>
+  </si>
+  <si>
+    <t>127,2</t>
+  </si>
+  <si>
+    <t>76,49</t>
+  </si>
+  <si>
+    <t>77,52</t>
+  </si>
+  <si>
+    <t>96,02</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>744,0</t>
+  </si>
+  <si>
+    <t>96,04</t>
+  </si>
+  <si>
+    <t>114,3</t>
+  </si>
+  <si>
+    <t>128,4</t>
+  </si>
+  <si>
+    <t>76,26</t>
+  </si>
+  <si>
+    <t>78,21</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>745,0</t>
+  </si>
+  <si>
+    <t>95,44</t>
+  </si>
+  <si>
+    <t>114,4</t>
+  </si>
+  <si>
+    <t>127,9</t>
+  </si>
+  <si>
+    <t>76,37</t>
+  </si>
+  <si>
+    <t>78,04</t>
+  </si>
+  <si>
+    <t>96,86</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>744,5</t>
+  </si>
+  <si>
+    <t>95,60</t>
+  </si>
+  <si>
+    <t>113,8</t>
+  </si>
+  <si>
+    <t>76,74</t>
+  </si>
+  <si>
+    <t>77,62</t>
+  </si>
+  <si>
+    <t>95,81</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>96,84</t>
+  </si>
+  <si>
+    <t>127,8</t>
+  </si>
+  <si>
+    <t>77,54</t>
+  </si>
+  <si>
+    <t>77,33</t>
+  </si>
+  <si>
+    <t>96,03</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>744,8</t>
+  </si>
+  <si>
+    <t>96,61</t>
   </si>
   <si>
     <t>113,9</t>
   </si>
   <si>
-    <t>123,5</t>
-  </si>
-  <si>
-    <t>78,82</t>
-  </si>
-  <si>
-    <t>79,15</t>
-  </si>
-  <si>
-    <t>98,21</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>-721,3</t>
-  </si>
-  <si>
-    <t>92,25</t>
+    <t>77,17</t>
+  </si>
+  <si>
+    <t>77,81</t>
+  </si>
+  <si>
+    <t>96,73</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>744,2</t>
+  </si>
+  <si>
+    <t>95,74</t>
+  </si>
+  <si>
+    <t>114,7</t>
+  </si>
+  <si>
+    <t>128,5</t>
+  </si>
+  <si>
+    <t>76,32</t>
+  </si>
+  <si>
+    <t>77,96</t>
+  </si>
+  <si>
+    <t>96,26</t>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>743,7</t>
+  </si>
+  <si>
+    <t>95,23</t>
+  </si>
+  <si>
+    <t>114,0</t>
+  </si>
+  <si>
+    <t>127,3</t>
+  </si>
+  <si>
+    <t>76,48</t>
+  </si>
+  <si>
+    <t>77,72</t>
+  </si>
+  <si>
+    <t>95,99</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>96,75</t>
+  </si>
+  <si>
+    <t>113,5</t>
+  </si>
+  <si>
+    <t>76,91</t>
+  </si>
+  <si>
+    <t>77,67</t>
+  </si>
+  <si>
+    <t>95,86</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>742,9</t>
+  </si>
+  <si>
+    <t>94,86</t>
+  </si>
+  <si>
+    <t>127,4</t>
+  </si>
+  <si>
+    <t>76,04</t>
+  </si>
+  <si>
+    <t>77,41</t>
+  </si>
+  <si>
+    <t>96,32</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>95,66</t>
+  </si>
+  <si>
+    <t>114,2</t>
+  </si>
+  <si>
+    <t>128,0</t>
+  </si>
+  <si>
+    <t>76,31</t>
+  </si>
+  <si>
+    <t>77,82</t>
+  </si>
+  <si>
+    <t>95,87</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>127,5</t>
+  </si>
+  <si>
+    <t>76,78</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>743,4</t>
+  </si>
+  <si>
+    <t>96,18</t>
+  </si>
+  <si>
+    <t>76,35</t>
+  </si>
+  <si>
+    <t>77,61</t>
+  </si>
+  <si>
+    <t>96,23</t>
+  </si>
+  <si>
+    <t>2,6</t>
+  </si>
+  <si>
+    <t>129,2</t>
+  </si>
+  <si>
+    <t>76,47</t>
+  </si>
+  <si>
+    <t>77,98</t>
+  </si>
+  <si>
+    <t>95,75</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>95,30</t>
+  </si>
+  <si>
+    <t>114,8</t>
+  </si>
+  <si>
+    <t>128,7</t>
+  </si>
+  <si>
+    <t>75,57</t>
+  </si>
+  <si>
+    <t>3,0</t>
+  </si>
+  <si>
+    <t>742,4</t>
+  </si>
+  <si>
+    <t>95,89</t>
   </si>
   <si>
     <t>113,7</t>
   </si>
   <si>
-    <t>123,6</t>
-  </si>
-  <si>
-    <t>78,58</t>
-  </si>
-  <si>
-    <t>78,99</t>
-  </si>
-  <si>
-    <t>98,09</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>-722,3</t>
-  </si>
-  <si>
-    <t>92,37</t>
-  </si>
-  <si>
-    <t>113,4</t>
-  </si>
-  <si>
-    <t>122,9</t>
-  </si>
-  <si>
-    <t>79,37</t>
-  </si>
-  <si>
-    <t>78,64</t>
-  </si>
-  <si>
-    <t>97,99</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>91,52</t>
-  </si>
-  <si>
-    <t>123,4</t>
-  </si>
-  <si>
-    <t>78,21</t>
-  </si>
-  <si>
-    <t>98,13</t>
-  </si>
-  <si>
-    <t>0,8</t>
-  </si>
-  <si>
-    <t>92,58</t>
-  </si>
-  <si>
-    <t>114,4</t>
-  </si>
-  <si>
-    <t>124,4</t>
-  </si>
-  <si>
-    <t>78,65</t>
-  </si>
-  <si>
-    <t>78,70</t>
-  </si>
-  <si>
-    <t>97,91</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>-722,6</t>
-  </si>
-  <si>
-    <t>92,60</t>
-  </si>
-  <si>
-    <t>114,0</t>
-  </si>
-  <si>
-    <t>124,0</t>
-  </si>
-  <si>
-    <t>78,72</t>
-  </si>
-  <si>
-    <t>79,12</t>
-  </si>
-  <si>
-    <t>98,19</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>91,69</t>
-  </si>
-  <si>
-    <t>113,3</t>
-  </si>
-  <si>
-    <t>122,7</t>
-  </si>
-  <si>
-    <t>78,71</t>
-  </si>
-  <si>
-    <t>78,59</t>
-  </si>
-  <si>
-    <t>98,55</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>92,51</t>
-  </si>
-  <si>
-    <t>123,8</t>
-  </si>
-  <si>
-    <t>78,79</t>
-  </si>
-  <si>
-    <t>78,86</t>
-  </si>
-  <si>
-    <t>98,46</t>
-  </si>
-  <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>91,76</t>
-  </si>
-  <si>
-    <t>113,8</t>
-  </si>
-  <si>
-    <t>98,35</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>-720,5</t>
-  </si>
-  <si>
-    <t>92,34</t>
-  </si>
-  <si>
-    <t>79,00</t>
-  </si>
-  <si>
-    <t>79,04</t>
-  </si>
-  <si>
-    <t>97,95</t>
-  </si>
-  <si>
-    <t>2,0</t>
-  </si>
-  <si>
-    <t>-720,7</t>
-  </si>
-  <si>
-    <t>91,98</t>
-  </si>
-  <si>
-    <t>113,5</t>
-  </si>
-  <si>
-    <t>123,3</t>
-  </si>
-  <si>
-    <t>78,42</t>
-  </si>
-  <si>
-    <t>97,72</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>-721,0</t>
-  </si>
-  <si>
-    <t>113,1</t>
-  </si>
-  <si>
-    <t>78,94</t>
-  </si>
-  <si>
-    <t>79,32</t>
-  </si>
-  <si>
-    <t>97,74</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>-722,1</t>
-  </si>
-  <si>
-    <t>91,80</t>
-  </si>
-  <si>
-    <t>122,6</t>
-  </si>
-  <si>
-    <t>78,63</t>
-  </si>
-  <si>
-    <t>97,75</t>
-  </si>
-  <si>
-    <t>2,6</t>
-  </si>
-  <si>
-    <t>91,54</t>
-  </si>
-  <si>
-    <t>78,53</t>
-  </si>
-  <si>
-    <t>2,8</t>
-  </si>
-  <si>
-    <t>91,83</t>
-  </si>
-  <si>
-    <t>78,56</t>
-  </si>
-  <si>
-    <t>78,80</t>
-  </si>
-  <si>
-    <t>98,16</t>
-  </si>
-  <si>
-    <t>3,0</t>
-  </si>
-  <si>
-    <t>-720,2</t>
-  </si>
-  <si>
-    <t>92,13</t>
-  </si>
-  <si>
-    <t>122,4</t>
-  </si>
-  <si>
-    <t>79,33</t>
-  </si>
-  <si>
-    <t>98,20</t>
+    <t>127,1</t>
+  </si>
+  <si>
+    <t>77,25</t>
+  </si>
+  <si>
+    <t>77,58</t>
+  </si>
+  <si>
+    <t>96,09</t>
   </si>
   <si>
     <t>3,2</t>
   </si>
   <si>
-    <t>91,89</t>
-  </si>
-  <si>
-    <t>113,6</t>
-  </si>
-  <si>
-    <t>78,97</t>
-  </si>
-  <si>
-    <t>78,91</t>
-  </si>
-  <si>
-    <t>97,71</t>
+    <t>78,14</t>
+  </si>
+  <si>
+    <t>96,00</t>
   </si>
   <si>
     <t>3,4</t>
   </si>
   <si>
-    <t>91,62</t>
-  </si>
-  <si>
-    <t>123,1</t>
-  </si>
-  <si>
-    <t>78,66</t>
-  </si>
-  <si>
-    <t>78,75</t>
-  </si>
-  <si>
-    <t>98,42</t>
+    <t>96,17</t>
+  </si>
+  <si>
+    <t>127,7</t>
+  </si>
+  <si>
+    <t>76,77</t>
+  </si>
+  <si>
+    <t>77,88</t>
+  </si>
+  <si>
+    <t>96,08</t>
   </si>
   <si>
     <t>3,6</t>
   </si>
   <si>
-    <t>92,50</t>
-  </si>
-  <si>
-    <t>114,1</t>
-  </si>
-  <si>
-    <t>78,95</t>
+    <t>95,02</t>
+  </si>
+  <si>
+    <t>113,2</t>
+  </si>
+  <si>
+    <t>126,6</t>
+  </si>
+  <si>
+    <t>76,33</t>
+  </si>
+  <si>
+    <t>77,73</t>
+  </si>
+  <si>
+    <t>96,13</t>
   </si>
   <si>
     <t>3,8</t>
   </si>
   <si>
-    <t>-721,8</t>
-  </si>
-  <si>
-    <t>92,78</t>
-  </si>
-  <si>
-    <t>79,35</t>
-  </si>
-  <si>
-    <t>78,69</t>
-  </si>
-  <si>
-    <t>97,70</t>
+    <t>95,88</t>
+  </si>
+  <si>
+    <t>76,90</t>
+  </si>
+  <si>
+    <t>78,22</t>
+  </si>
+  <si>
+    <t>95,79</t>
   </si>
 </sst>
 </file>
@@ -829,7 +844,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -837,7 +852,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.59402777777777771</v>
+        <v>0.7709259259259259</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -978,7 +993,7 @@
         <v>34</v>
       </c>
       <c r="C23">
-        <v>2723</v>
+        <v>1065</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -1007,7 +1022,7 @@
         <v>42</v>
       </c>
       <c r="C24">
-        <v>2724</v>
+        <v>1062</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -1025,82 +1040,82 @@
         <v>47</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
         <v>49</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25">
+        <v>1064</v>
+      </c>
+      <c r="D25" t="s">
         <v>50</v>
       </c>
-      <c r="C25">
-        <v>2724</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>51</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>52</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>53</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>54</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>55</v>
-      </c>
-      <c r="I25" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
         <v>57</v>
       </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
       <c r="C26">
-        <v>2726</v>
+        <v>1065</v>
       </c>
       <c r="D26" t="s">
         <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="G26" t="s">
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="I26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C27">
-        <v>2725</v>
+        <v>1063</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F27" t="s">
         <v>65</v>
@@ -1123,7 +1138,7 @@
         <v>70</v>
       </c>
       <c r="C28">
-        <v>2723</v>
+        <v>1065</v>
       </c>
       <c r="D28" t="s">
         <v>71</v>
@@ -1132,27 +1147,27 @@
         <v>72</v>
       </c>
       <c r="F28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" t="s">
         <v>73</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>74</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>75</v>
-      </c>
-      <c r="I28" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
         <v>77</v>
       </c>
-      <c r="B29" t="s">
-        <v>50</v>
-      </c>
       <c r="C29">
-        <v>2722</v>
+        <v>1063</v>
       </c>
       <c r="D29" t="s">
         <v>78</v>
@@ -1178,376 +1193,376 @@
         <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="C30">
-        <v>2723</v>
+        <v>1064</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C31">
-        <v>2724</v>
+        <v>1065</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="I31" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C32">
-        <v>2724</v>
+        <v>1063</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="G32" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H32" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I32" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C33">
-        <v>2725</v>
+        <v>1064</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F33" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G33" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H33" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="I33" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="C34">
-        <v>2724</v>
+        <v>1063</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="G34" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H34" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="I34" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C35">
-        <v>2723</v>
+        <v>1063</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="F35" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="G35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H35" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="I35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="C36">
-        <v>2724</v>
+        <v>1067</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="E36" t="s">
         <v>79</v>
       </c>
       <c r="F36" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H36" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="I36" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C37">
-        <v>2724</v>
+        <v>1063</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="G37" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
-        <v>126</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C38">
-        <v>2725</v>
+        <v>1063</v>
       </c>
       <c r="D38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="F38" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G38" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H38" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="I38" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="C39">
-        <v>2726</v>
+        <v>1064</v>
       </c>
       <c r="D39" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" t="s">
         <v>134</v>
       </c>
-      <c r="E39" t="s">
-        <v>135</v>
-      </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="H39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="C40">
-        <v>2724</v>
+        <v>1064</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F40" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H40" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I40" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="C41">
-        <v>2724</v>
+        <v>1063</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F41" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="G41" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H41" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="I41" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="C42">
-        <v>2722</v>
+        <v>1064</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E42" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="F42" t="s">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H42" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I42" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
